--- a/experiments/experiments_centralized.xlsx
+++ b/experiments/experiments_centralized.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eashw\Desktop\post_graduation_plan\Collaborations\Swarm_collaboration_via_stigmergy\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC21619D-FCBB-432E-8693-7B37A455F62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A338AE-76D1-4DE3-95F5-952CB88D27B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="detailed" sheetId="1" r:id="rId1"/>
     <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>grid_size</t>
   </si>
@@ -32,6 +32,18 @@
     <t>n_failures</t>
   </si>
   <si>
+    <t>targets</t>
+  </si>
+  <si>
+    <t>failed_robot_ids</t>
+  </si>
+  <si>
+    <t>fail_steps</t>
+  </si>
+  <si>
+    <t>steps_to_complete</t>
+  </si>
+  <si>
     <t>runs</t>
   </si>
   <si>
@@ -39,49 +51,13 @@
   </si>
   <si>
     <t>std_steps</t>
-  </si>
-  <si>
-    <t>targets</t>
-  </si>
-  <si>
-    <t>failed_robot_ids</t>
-  </si>
-  <si>
-    <t>fail_steps</t>
-  </si>
-  <si>
-    <t>steps_to_complete</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>1;0</t>
-  </si>
-  <si>
-    <t>38;77</t>
-  </si>
-  <si>
-    <t>9;12;4;10</t>
-  </si>
-  <si>
-    <t>19;21;52;91</t>
-  </si>
-  <si>
-    <t>4;17;19;9;12;3</t>
-  </si>
-  <si>
-    <t>26;43;52;77;97;179</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,15 +68,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,7 +82,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,43 +92,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -177,9 +132,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -217,7 +172,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -289,7 +244,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -310,6 +265,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -320,31 +276,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -366,7 +322,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -424,7 +380,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -437,12 +393,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -461,22 +418,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.68359375" customWidth="1"/>
+    <col min="2" max="2" width="10.68359375" customWidth="1"/>
+    <col min="3" max="3" width="9.68359375" customWidth="1"/>
+    <col min="4" max="4" width="18.68359375" customWidth="1"/>
+    <col min="5" max="5" width="12.68359375" customWidth="1"/>
+    <col min="6" max="6" width="19.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,134 +437,93 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>200</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>300</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>400</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>500</v>
+      </c>
+      <c r="B5">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2">
-        <v>50</v>
-      </c>
-      <c r="B3" s="2">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="2">
-        <v>75</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2">
-        <v>100</v>
-      </c>
-      <c r="B5" s="2">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2">
-        <v>150</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2">
-        <v>704</v>
+      <c r="F5">
+        <v>3118</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.68359375" customWidth="1"/>
+    <col min="2" max="2" width="10.68359375" customWidth="1"/>
+    <col min="3" max="3" width="12.68359375" customWidth="1"/>
+    <col min="4" max="4" width="6.68359375" customWidth="1"/>
+    <col min="5" max="6" width="11.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,92 +534,92 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>200</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1512</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>300</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2686</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>400</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3322</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>500</v>
+      </c>
+      <c r="B5">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>104</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2">
-        <v>50</v>
-      </c>
-      <c r="B3" s="2">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>317</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="2">
-        <v>75</v>
-      </c>
-      <c r="B4" s="2">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>567</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2">
-        <v>100</v>
-      </c>
-      <c r="B5" s="2">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>704</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="E5">
+        <v>3118</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
